--- a/testdata/mobile/CheckInOut.xlsx
+++ b/testdata/mobile/CheckInOut.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Sales Force\Automation\stp-automation-test\testdata\mobile\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Sales Force\Automation\sales-force-automation-test\testdata\mobile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AD7C9C0-740B-46F8-8137-6BD6D11ECFFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D56218C2-5180-40DB-8F9E-C468FFD09B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -75,12 +75,6 @@
     <t>checkin</t>
   </si>
   <si>
-    <t>-6.164869236680177</t>
-  </si>
-  <si>
-    <t>106.76341189956153</t>
-  </si>
-  <si>
     <t>Pending</t>
   </si>
   <si>
@@ -90,12 +84,6 @@
     <t>/testdata/images/product1.jpg</t>
   </si>
   <si>
-    <t>-6.23830201419125</t>
-  </si>
-  <si>
-    <t>106.78328452604089</t>
-  </si>
-  <si>
     <t>Cabang Kebayoran Lama</t>
   </si>
   <si>
@@ -108,12 +96,6 @@
     <t>Cabang Permata Hijau</t>
   </si>
   <si>
-    <t>-6.218303889480235</t>
-  </si>
-  <si>
-    <t>106.77826786492784</t>
-  </si>
-  <si>
     <t>cancel</t>
   </si>
   <si>
@@ -133,6 +115,24 @@
   </si>
   <si>
     <t>Smart Watch and Camera,2,3500000</t>
+  </si>
+  <si>
+    <t>-6.1648863244805625</t>
+  </si>
+  <si>
+    <t>106.76346571069685</t>
+  </si>
+  <si>
+    <t>-6.217946979432403</t>
+  </si>
+  <si>
+    <t>106.77798395302567</t>
+  </si>
+  <si>
+    <t>-6.238259352967404</t>
+  </si>
+  <si>
+    <t>106.78330598371257</t>
   </si>
 </sst>
 </file>
@@ -489,24 +489,24 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -514,13 +514,13 @@
         <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
         <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -545,10 +545,10 @@
         <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -556,16 +556,16 @@
         <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
         <v>11</v>
@@ -576,19 +576,19 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s">
         <v>16</v>
       </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
       <c r="F6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -601,16 +601,16 @@
         <v>9</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -623,16 +623,16 @@
         <v>9</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F8" t="s">
         <v>11</v>
       </c>
       <c r="G8" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/mobile/CheckInOut.xlsx
+++ b/testdata/mobile/CheckInOut.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Sales Force\Automation\sales-force-automation-test\testdata\mobile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D56218C2-5180-40DB-8F9E-C468FFD09B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{295357B8-8231-4413-8CB1-4F9313F11914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
   <si>
     <t>longtitude</t>
   </si>
@@ -66,12 +66,6 @@
     <t>In Progress</t>
   </si>
   <si>
-    <t>Cabang Green Garden</t>
-  </si>
-  <si>
-    <t>Lumoshive</t>
-  </si>
-  <si>
     <t>checkin</t>
   </si>
   <si>
@@ -81,9 +75,6 @@
     <t>Assigned</t>
   </si>
   <si>
-    <t>/testdata/images/product1.jpg</t>
-  </si>
-  <si>
     <t>Cabang Kebayoran Lama</t>
   </si>
   <si>
@@ -93,9 +84,6 @@
     <t>/testdata/images/product2.jpg</t>
   </si>
   <si>
-    <t>Cabang Permata Hijau</t>
-  </si>
-  <si>
     <t>cancel</t>
   </si>
   <si>
@@ -108,25 +96,7 @@
     <t>Cabang Pondok Indah</t>
   </si>
   <si>
-    <t>Smart Watch and Camera,1,50000;Sun Screen,5,10000</t>
-  </si>
-  <si>
     <t>Sun Screen,3,50000</t>
-  </si>
-  <si>
-    <t>Smart Watch and Camera,2,3500000</t>
-  </si>
-  <si>
-    <t>-6.1648863244805625</t>
-  </si>
-  <si>
-    <t>106.76346571069685</t>
-  </si>
-  <si>
-    <t>-6.217946979432403</t>
-  </si>
-  <si>
-    <t>106.77798395302567</t>
   </si>
   <si>
     <t>-6.238259352967404</t>
@@ -451,7 +421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99B07047-0310-47A7-8331-365963E4E0F7}">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.44140625" bestFit="1" customWidth="1"/>
@@ -489,44 +459,44 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
         <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -539,100 +509,16 @@
         <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
